--- a/artfynd/A 60162-2020 artfynd.xlsx
+++ b/artfynd/A 60162-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60162-2020 artfynd.xlsx
+++ b/artfynd/A 60162-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1492,755 +1492,6 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>112605822</v>
-      </c>
-      <c r="B9" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Gåssjö, Hls</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>518382</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6883360</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Ramsjö</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>112605823</v>
-      </c>
-      <c r="B10" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Gåssjö, Hls</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>518366</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6883388</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Ramsjö</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>112605824</v>
-      </c>
-      <c r="B11" t="n">
-        <v>78920</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Gåssjö, Hls</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>518357</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6883395</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Ramsjö</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>112605819</v>
-      </c>
-      <c r="B12" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Gåssjö, Hls</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>518352</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6883378</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Ramsjö</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>112605820</v>
-      </c>
-      <c r="B13" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Gåssjö, Hls</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>518352</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6883381</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Ramsjö</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>112605821</v>
-      </c>
-      <c r="B14" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Gåssjö, Hls</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>518397</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6883354</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Ramsjö</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>112605817</v>
-      </c>
-      <c r="B15" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Gåssjö, Hls</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>518312</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6882962</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Ramsjö</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
